--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260828.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260828.xlsx
@@ -953,17 +953,17 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>神達控股</t>
+          <t>技嘉科技</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>36,304,000</t>
+          <t>9,588,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -975,17 +975,17 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>技嘉科技</t>
+          <t>神達控股</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>9,588,000</t>
+          <t>36,304,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>M_NTD</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>英業達股</t>
+          <t>MARGIN</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>41,037,000</t>
+          <t>2,675,121,747</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>M_NTD</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>MARGIN</t>
+          <t>英業達股</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>2,675,121,747</t>
+          <t>41,037,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>鴻海精密</t>
+          <t>健鼎科技</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>9,652,000</t>
+          <t>4,984,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>健鼎科技</t>
+          <t>鴻海精密</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>4,984,000</t>
+          <t>9,652,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
